--- a/testDjangosite/media/excel_files/listregion/listregionfilters_73.xlsx
+++ b/testDjangosite/media/excel_files/listregion/listregionfilters_73.xlsx
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J8"/>
+  <dimension ref="A1:J5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="30" customHeight="1"/>
@@ -500,11 +500,11 @@
         <v>0</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>693</v>
+        <v>6</v>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>2025-06-24</t>
+          <t>2025-07-31</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -524,7 +524,7 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -533,11 +533,11 @@
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -546,40 +546,40 @@
         <v>1</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>699</v>
+        <v>5</v>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>2025-07-06</t>
+          <t>2025-03-13</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Асиновское</t>
+          <t>Красноярское</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Асиновское</t>
+          <t>Ижморское</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Томская область</t>
+          <t>Кемеровская область</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>Светлое</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>55</v>
+        <v>11.6</v>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
@@ -592,44 +592,44 @@
         <v>2</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>700</v>
+        <v>4</v>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>2025-07-06</t>
+          <t>2025-03-13</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Бакчарское</t>
+          <t>Берикульское</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Бакчарское</t>
+          <t>Тисульское</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Томская область</t>
+          <t>Кемеровская область</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Первое</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>19</t>
         </is>
       </c>
     </row>
@@ -638,185 +638,48 @@
         <v>3</v>
       </c>
       <c r="B5" s="2" t="n">
-        <v>701</v>
+        <v>3</v>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2025-07-06</t>
+          <t>2025-03-13</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Катайгинское</t>
+          <t>Берикульское</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Верхнекетское</t>
+          <t>Тисульское</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Томская область</t>
+          <t>Кемеровская область</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>Первое</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="30" customHeight="1">
-      <c r="A6" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="B6" s="2" t="n">
-        <v>540</v>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>2025-03-13</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>Красноярское</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>Ижморское</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>Кемеровская область</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>Светлое</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="n">
-        <v>11.6</v>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="B7" s="2" t="n">
-        <v>539</v>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>2025-03-13</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>Берикульское</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>Тисульское</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>Кемеровская область</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>Первое</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
           <t>19</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="B8" s="2" t="n">
-        <v>538</v>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>2025-03-13</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>Берикульское</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>Тисульское</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>Кемеровская область</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>Первое</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-    </row>
+    <row r="6" ht="30" customHeight="1"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -828,7 +691,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I8"/>
+  <dimension ref="A1:I5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="30" customHeight="1"/>
@@ -881,12 +744,12 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>693</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>2025-06-24</t>
+          <t>2025-07-31</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -906,7 +769,7 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -916,7 +779,7 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -926,37 +789,37 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>699</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>2025-07-06</t>
+          <t>2025-03-13</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Асиновское</t>
+          <t>Красноярское</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Асиновское</t>
+          <t>Ижморское</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Томская область</t>
+          <t>Кемеровская область</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>Светлое</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
@@ -971,42 +834,42 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>700</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>2025-07-06</t>
+          <t>2025-03-13</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Бакчарское</t>
+          <t>Берикульское</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Бакчарское</t>
+          <t>Тисульское</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Томская область</t>
+          <t>Кемеровская область</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Первое</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>19</t>
         </is>
       </c>
     </row>
@@ -1016,180 +879,46 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>701</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2025-07-06</t>
+          <t>2025-03-13</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Катайгинское</t>
+          <t>Берикульское</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Верхнекетское</t>
+          <t>Тисульское</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Томская область</t>
+          <t>Кемеровская область</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>Первое</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="30" customHeight="1">
-      <c r="A6" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>540</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>2025-03-13</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>Красноярское</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>Ижморское</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>Кемеровская область</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>Светлое</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>539</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>2025-03-13</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>Берикульское</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>Тисульское</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>Кемеровская область</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>Первое</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
           <t>19</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>538</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>2025-03-13</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>Берикульское</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>Тисульское</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>Кемеровская область</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>Первое</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-    </row>
+    <row r="6" ht="30" customHeight="1"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1201,7 +930,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I8"/>
+  <dimension ref="A1:I5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="30" customHeight="1"/>
@@ -1254,12 +983,12 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>693</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>2025-06-24</t>
+          <t>2025-07-31</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -1279,7 +1008,7 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -1289,7 +1018,7 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -1299,37 +1028,37 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>699</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>2025-07-06</t>
+          <t>2025-03-13</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Асиновское</t>
+          <t>Красноярское</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Асиновское</t>
+          <t>Ижморское</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Томская область</t>
+          <t>Кемеровская область</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>Светлое</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
@@ -1344,42 +1073,42 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>700</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>2025-07-06</t>
+          <t>2025-03-13</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Бакчарское</t>
+          <t>Берикульское</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Бакчарское</t>
+          <t>Тисульское</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Томская область</t>
+          <t>Кемеровская область</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Первое</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>19</t>
         </is>
       </c>
     </row>
@@ -1389,180 +1118,46 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>701</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2025-07-06</t>
+          <t>2025-03-13</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Катайгинское</t>
+          <t>Берикульское</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Верхнекетское</t>
+          <t>Тисульское</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Томская область</t>
+          <t>Кемеровская область</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>Первое</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="30" customHeight="1">
-      <c r="A6" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>540</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>2025-03-13</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>Красноярское</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>Ижморское</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>Кемеровская область</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>Светлое</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>539</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>2025-03-13</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>Берикульское</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>Тисульское</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>Кемеровская область</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>Первое</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
           <t>19</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>538</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>2025-03-13</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>Берикульское</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>Тисульское</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>Кемеровская область</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>Первое</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-    </row>
+    <row r="6" ht="30" customHeight="1"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1574,7 +1169,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R9"/>
+  <dimension ref="A1:R6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7.199999999999999" customWidth="1" min="1" max="1"/>
@@ -1589,7 +1184,7 @@
     <col width="16.8" customWidth="1" min="10" max="10"/>
     <col width="18" customWidth="1" min="11" max="11"/>
     <col width="9.6" customWidth="1" min="12" max="12"/>
-    <col width="19.2" customWidth="1" min="13" max="13"/>
+    <col width="14.4" customWidth="1" min="13" max="13"/>
     <col width="42" customWidth="1" min="14" max="14"/>
     <col width="40.8" customWidth="1" min="15" max="15"/>
     <col width="8.4" customWidth="1" min="16" max="16"/>
@@ -1661,7 +1256,7 @@
       </c>
       <c r="M2" s="4" t="inlineStr">
         <is>
-          <t>Категория, год</t>
+          <t>Категория</t>
         </is>
       </c>
       <c r="N2" s="4" t="inlineStr">
@@ -1692,11 +1287,11 @@
     </row>
     <row r="3">
       <c r="A3" s="4" t="n">
-        <v>693</v>
+        <v>6</v>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>2025-06-24</t>
+          <t>2025-07-31</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
@@ -1711,12 +1306,12 @@
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G3" s="4" t="inlineStr">
@@ -1725,24 +1320,24 @@
         </is>
       </c>
       <c r="H3" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I3" s="4" t="n"/>
       <c r="J3" s="4" t="n"/>
-      <c r="K3" s="4" t="n"/>
-      <c r="L3" s="4" t="n">
+      <c r="K3" s="4" t="n">
         <v>2025</v>
       </c>
+      <c r="L3" s="4" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
       <c r="M3" s="4" t="inlineStr">
         <is>
-          <t>Нет</t>
-        </is>
-      </c>
-      <c r="N3" s="4" t="inlineStr">
-        <is>
           <t>вырубка</t>
         </is>
       </c>
+      <c r="N3" s="4" t="n"/>
       <c r="O3" s="4" t="inlineStr">
         <is>
           <t>искусственное лесовосстановление</t>
@@ -1751,7 +1346,7 @@
       <c r="P3" s="4" t="n"/>
       <c r="Q3" s="4" t="inlineStr">
         <is>
-          <t>Уточнить</t>
+          <t>Соответствует</t>
         </is>
       </c>
       <c r="R3" s="4" t="inlineStr">
@@ -1762,26 +1357,26 @@
     </row>
     <row r="4">
       <c r="A4" s="4" t="n">
-        <v>699</v>
+        <v>5</v>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>2025-07-06</t>
+          <t>2025-03-13</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>Асиновское</t>
+          <t>Ижморское</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>Асиновское</t>
+          <t>Красноярское</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>Светлое</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
@@ -1791,37 +1386,41 @@
       </c>
       <c r="G4" s="4" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>15</t>
         </is>
       </c>
       <c r="H4" s="4" t="n">
-        <v>55</v>
+        <v>11.6</v>
       </c>
       <c r="I4" s="4" t="n"/>
       <c r="J4" s="4" t="n"/>
-      <c r="K4" s="4" t="n"/>
-      <c r="L4" s="4" t="n">
+      <c r="K4" s="4" t="n">
         <v>2025</v>
       </c>
+      <c r="L4" s="4" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
       <c r="M4" s="4" t="inlineStr">
         <is>
-          <t>Нет</t>
-        </is>
-      </c>
-      <c r="N4" s="4" t="inlineStr">
-        <is>
-          <t>Не указано</t>
-        </is>
-      </c>
+          <t>вырубка</t>
+        </is>
+      </c>
+      <c r="N4" s="4" t="n"/>
       <c r="O4" s="4" t="inlineStr">
         <is>
-          <t>Не указано</t>
-        </is>
-      </c>
-      <c r="P4" s="4" t="n"/>
+          <t>искусственное лесовосстановление</t>
+        </is>
+      </c>
+      <c r="P4" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="Q4" s="4" t="inlineStr">
         <is>
-          <t>Уточнить</t>
+          <t>Соответствует</t>
         </is>
       </c>
       <c r="R4" s="4" t="inlineStr">
@@ -1832,57 +1431,57 @@
     </row>
     <row r="5">
       <c r="A5" s="4" t="n">
-        <v>700</v>
+        <v>4</v>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>2025-07-06</t>
+          <t>2025-03-13</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>Бакчарское</t>
+          <t>Тисульское</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>Бакчарское</t>
+          <t>Берикульское</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Первое</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>19</t>
         </is>
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>18</t>
         </is>
       </c>
       <c r="H5" s="4" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="I5" s="4" t="n"/>
       <c r="J5" s="4" t="n"/>
-      <c r="K5" s="4" t="n"/>
-      <c r="L5" s="4" t="n">
+      <c r="K5" s="4" t="n">
         <v>2025</v>
       </c>
+      <c r="L5" s="4" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
       <c r="M5" s="4" t="inlineStr">
         <is>
-          <t>Нет</t>
-        </is>
-      </c>
-      <c r="N5" s="4" t="inlineStr">
-        <is>
           <t>Не указано</t>
         </is>
       </c>
+      <c r="N5" s="4" t="n"/>
       <c r="O5" s="4" t="inlineStr">
         <is>
           <t>Не указано</t>
@@ -1891,7 +1490,7 @@
       <c r="P5" s="4" t="n"/>
       <c r="Q5" s="4" t="inlineStr">
         <is>
-          <t>Уточнить</t>
+          <t>Соответствует</t>
         </is>
       </c>
       <c r="R5" s="4" t="inlineStr">
@@ -1902,57 +1501,57 @@
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
-        <v>701</v>
+        <v>3</v>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>2025-07-06</t>
+          <t>2025-03-13</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>Верхнекетское</t>
+          <t>Тисульское</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>Катайгинское</t>
+          <t>Берикульское</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>Первое</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>19</t>
         </is>
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>18</t>
         </is>
       </c>
       <c r="H6" s="4" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="I6" s="4" t="n"/>
       <c r="J6" s="4" t="n"/>
-      <c r="K6" s="4" t="n"/>
-      <c r="L6" s="4" t="n">
+      <c r="K6" s="4" t="n">
         <v>2025</v>
       </c>
+      <c r="L6" s="4" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
       <c r="M6" s="4" t="inlineStr">
         <is>
-          <t>Нет</t>
-        </is>
-      </c>
-      <c r="N6" s="4" t="inlineStr">
-        <is>
           <t>Не указано</t>
         </is>
       </c>
+      <c r="N6" s="4" t="n"/>
       <c r="O6" s="4" t="inlineStr">
         <is>
           <t>Не указано</t>
@@ -1961,220 +1560,10 @@
       <c r="P6" s="4" t="n"/>
       <c r="Q6" s="4" t="inlineStr">
         <is>
-          <t>Уточнить</t>
+          <t>Соответствует</t>
         </is>
       </c>
       <c r="R6" s="4" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="4" t="n">
-        <v>540</v>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>2025-03-13</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>Ижморское</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>Красноярское</t>
-        </is>
-      </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>Светлое</t>
-        </is>
-      </c>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="G7" s="4" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="H7" s="4" t="n">
-        <v>11.6</v>
-      </c>
-      <c r="I7" s="4" t="n"/>
-      <c r="J7" s="4" t="n"/>
-      <c r="K7" s="4" t="n"/>
-      <c r="L7" s="4" t="n">
-        <v>2025</v>
-      </c>
-      <c r="M7" s="4" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-      <c r="N7" s="4" t="inlineStr">
-        <is>
-          <t>вырубка</t>
-        </is>
-      </c>
-      <c r="O7" s="4" t="inlineStr">
-        <is>
-          <t>искусственное лесовосстановление</t>
-        </is>
-      </c>
-      <c r="P7" s="4" t="n"/>
-      <c r="Q7" s="4" t="inlineStr">
-        <is>
-          <t>Уточнить</t>
-        </is>
-      </c>
-      <c r="R7" s="4" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="4" t="n">
-        <v>539</v>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>2025-03-13</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>Тисульское</t>
-        </is>
-      </c>
-      <c r="D8" s="4" t="inlineStr">
-        <is>
-          <t>Берикульское</t>
-        </is>
-      </c>
-      <c r="E8" s="4" t="inlineStr">
-        <is>
-          <t>Первое</t>
-        </is>
-      </c>
-      <c r="F8" s="4" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="G8" s="4" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="H8" s="4" t="n">
-        <v>11</v>
-      </c>
-      <c r="I8" s="4" t="n"/>
-      <c r="J8" s="4" t="n"/>
-      <c r="K8" s="4" t="n"/>
-      <c r="L8" s="4" t="n">
-        <v>2025</v>
-      </c>
-      <c r="M8" s="4" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-      <c r="N8" s="4" t="inlineStr">
-        <is>
-          <t>Не указано</t>
-        </is>
-      </c>
-      <c r="O8" s="4" t="inlineStr">
-        <is>
-          <t>Не указано</t>
-        </is>
-      </c>
-      <c r="P8" s="4" t="n"/>
-      <c r="Q8" s="4" t="inlineStr">
-        <is>
-          <t>Уточнить</t>
-        </is>
-      </c>
-      <c r="R8" s="4" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="4" t="n">
-        <v>538</v>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>2025-03-13</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>Тисульское</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="inlineStr">
-        <is>
-          <t>Берикульское</t>
-        </is>
-      </c>
-      <c r="E9" s="4" t="inlineStr">
-        <is>
-          <t>Первое</t>
-        </is>
-      </c>
-      <c r="F9" s="4" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="G9" s="4" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="H9" s="4" t="n">
-        <v>11</v>
-      </c>
-      <c r="I9" s="4" t="n"/>
-      <c r="J9" s="4" t="n"/>
-      <c r="K9" s="4" t="n"/>
-      <c r="L9" s="4" t="n">
-        <v>2025</v>
-      </c>
-      <c r="M9" s="4" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-      <c r="N9" s="4" t="inlineStr">
-        <is>
-          <t>Не указано</t>
-        </is>
-      </c>
-      <c r="O9" s="4" t="inlineStr">
-        <is>
-          <t>Не указано</t>
-        </is>
-      </c>
-      <c r="P9" s="4" t="n"/>
-      <c r="Q9" s="4" t="inlineStr">
-        <is>
-          <t>Уточнить</t>
-        </is>
-      </c>
-      <c r="R9" s="4" t="inlineStr">
         <is>
           <t>Нет</t>
         </is>
